--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -1289,45 +1289,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128707376</v>
+        <v>128706804</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andviken, Andviken, Mpd</t>
+          <t>Udden, Udden, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519695</v>
+        <v>519635</v>
       </c>
       <c r="R8" t="n">
-        <v>6920473</v>
+        <v>6920495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,45 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128706804</v>
+        <v>128707376</v>
       </c>
       <c r="B9" t="n">
-        <v>92756</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Udden, Udden, Mpd</t>
+          <t>Andviken, Andviken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519635</v>
+        <v>519695</v>
       </c>
       <c r="R9" t="n">
-        <v>6920495</v>
+        <v>6920473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128706823</v>
       </c>
       <c r="B2" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128707275</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128707136</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128706804</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128709713</v>
       </c>
       <c r="B10" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128708413</v>
       </c>
       <c r="B11" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128706823</v>
       </c>
       <c r="B2" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128710628</v>
       </c>
       <c r="B3" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128707275</v>
       </c>
       <c r="B4" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>128710147</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128707136</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128710276</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128706804</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128707376</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128709713</v>
       </c>
       <c r="B10" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128708413</v>
       </c>
       <c r="B11" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128706823</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128707275</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128707136</v>
       </c>
       <c r="B6" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128706804</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128709713</v>
       </c>
       <c r="B10" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128708413</v>
       </c>
       <c r="B11" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128706823</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128707275</v>
       </c>
       <c r="B4" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128707136</v>
       </c>
       <c r="B6" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128706804</v>
       </c>
       <c r="B8" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128709713</v>
       </c>
       <c r="B10" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128708413</v>
       </c>
       <c r="B11" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128706823</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128710628</v>
       </c>
       <c r="B3" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128707275</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>128710147</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128707136</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128710276</v>
       </c>
       <c r="B7" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128706804</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128707376</v>
       </c>
       <c r="B9" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128709713</v>
       </c>
       <c r="B10" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128708413</v>
       </c>
       <c r="B11" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128706823</v>
       </c>
       <c r="B2" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128710628</v>
       </c>
       <c r="B3" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128707275</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>128710147</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128707136</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128710276</v>
       </c>
       <c r="B7" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128706804</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128707376</v>
       </c>
       <c r="B9" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128709713</v>
       </c>
       <c r="B10" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128708413</v>
       </c>
       <c r="B11" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128706823</v>
       </c>
       <c r="B2" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128707275</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128707136</v>
       </c>
       <c r="B6" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128706804</v>
       </c>
       <c r="B8" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128709713</v>
       </c>
       <c r="B10" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128708413</v>
       </c>
       <c r="B11" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128706823</v>
       </c>
       <c r="B2" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128707275</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128707136</v>
       </c>
       <c r="B6" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,45 +1289,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128706804</v>
+        <v>128707376</v>
       </c>
       <c r="B8" t="n">
-        <v>92816</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Udden, Udden, Mpd</t>
+          <t>Andviken, Andviken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519635</v>
+        <v>519695</v>
       </c>
       <c r="R8" t="n">
-        <v>6920495</v>
+        <v>6920473</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,45 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128707376</v>
+        <v>128706804</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>92819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andviken, Andviken, Mpd</t>
+          <t>Udden, Udden, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519695</v>
+        <v>519635</v>
       </c>
       <c r="R9" t="n">
-        <v>6920473</v>
+        <v>6920495</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,7 +1486,7 @@
         <v>128709713</v>
       </c>
       <c r="B10" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128708413</v>
       </c>
       <c r="B11" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -1289,45 +1289,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128707376</v>
+        <v>128706804</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>92819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andviken, Andviken, Mpd</t>
+          <t>Udden, Udden, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519695</v>
+        <v>519635</v>
       </c>
       <c r="R8" t="n">
-        <v>6920473</v>
+        <v>6920495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,45 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128706804</v>
+        <v>128707376</v>
       </c>
       <c r="B9" t="n">
-        <v>92819</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Udden, Udden, Mpd</t>
+          <t>Andviken, Andviken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519635</v>
+        <v>519695</v>
       </c>
       <c r="R9" t="n">
-        <v>6920495</v>
+        <v>6920473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128706823</v>
       </c>
       <c r="B2" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128710628</v>
       </c>
       <c r="B3" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128707275</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>128710147</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128707136</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128710276</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128706804</v>
       </c>
       <c r="B8" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128707376</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128709713</v>
       </c>
       <c r="B10" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128708413</v>
       </c>
       <c r="B11" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128706823</v>
       </c>
       <c r="B2" t="n">
-        <v>92826</v>
+        <v>92835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128710628</v>
       </c>
       <c r="B3" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128707275</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>128710147</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128707136</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128710276</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,45 +1289,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128706804</v>
+        <v>128707376</v>
       </c>
       <c r="B8" t="n">
-        <v>92826</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Udden, Udden, Mpd</t>
+          <t>Andviken, Andviken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519635</v>
+        <v>519695</v>
       </c>
       <c r="R8" t="n">
-        <v>6920495</v>
+        <v>6920473</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,45 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128707376</v>
+        <v>128706804</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andviken, Andviken, Mpd</t>
+          <t>Udden, Udden, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519695</v>
+        <v>519635</v>
       </c>
       <c r="R9" t="n">
-        <v>6920473</v>
+        <v>6920495</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,7 +1486,7 @@
         <v>128709713</v>
       </c>
       <c r="B10" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128708413</v>
       </c>
       <c r="B11" t="n">
-        <v>92826</v>
+        <v>92835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>128710147</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>128710147</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29880-2025 artfynd.xlsx
+++ b/artfynd/A 29880-2025 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>128710147</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
